--- a/artfynd/A 40356-2025 artfynd.xlsx
+++ b/artfynd/A 40356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16739040</v>
       </c>
       <c r="B2" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,7 +690,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483720.3879121186</v>
+        <v>483720</v>
       </c>
       <c r="R2" t="n">
-        <v>6269912.245103796</v>
+        <v>6269912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +753,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -803,41 +788,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16739042</v>
+        <v>16739048</v>
       </c>
       <c r="B3" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4377</v>
+        <v>805</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483720.3879121186</v>
+        <v>483780</v>
       </c>
       <c r="R3" t="n">
-        <v>6269912.245103796</v>
+        <v>6270030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +866,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +899,7 @@
         <v>16739041</v>
       </c>
       <c r="B4" t="n">
-        <v>86166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +911,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -968,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483720.3879121186</v>
+        <v>483720</v>
       </c>
       <c r="R4" t="n">
-        <v>6269912.245103796</v>
+        <v>6269912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,19 +974,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16739043</v>
+        <v>16739044</v>
       </c>
       <c r="B5" t="n">
-        <v>86148</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4383</v>
+        <v>4373</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvaxskivling</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>(Wulfen) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483720.3879121186</v>
+        <v>483720</v>
       </c>
       <c r="R5" t="n">
-        <v>6269912.245103796</v>
+        <v>6269912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,19 +1074,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,53 +1104,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16739047</v>
+        <v>16739052</v>
       </c>
       <c r="B6" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220228</v>
+        <v>4373</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Wulfen) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tåget, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483720.3879121186</v>
+        <v>483780</v>
       </c>
       <c r="R6" t="n">
-        <v>6269912.245103796</v>
+        <v>6270030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,27 +1174,18 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16739044</v>
+        <v>16739046</v>
       </c>
       <c r="B7" t="n">
-        <v>86131</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4373</v>
+        <v>4374</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spröd vaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483720.3879121186</v>
+        <v>483720</v>
       </c>
       <c r="R7" t="n">
-        <v>6269912.245103796</v>
+        <v>6269912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,19 +1274,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,15 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16739046</v>
+        <v>16739051</v>
       </c>
       <c r="B8" t="n">
-        <v>86132</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1319,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1428,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483720.3879121186</v>
+        <v>483780</v>
       </c>
       <c r="R8" t="n">
-        <v>6269912.245103796</v>
+        <v>6270030</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,19 +1374,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,6 +1401,706 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16739042</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483720</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6269912</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16739053</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483780</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6270030</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>16739043</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4383</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Småvaxing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hygrocybe insipida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(J.E.Lange) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483720</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6269912</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16739049</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4383</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Småvaxing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrocybe insipida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(J.E.Lange) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483780</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6270030</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16739050</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89059</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4393</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Papegojvaxing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gliophorus psittacinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Herink</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483780</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6270030</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16739054</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89106</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4394</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Honungsvaxing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483780</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6270030</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16739047</v>
+      </c>
+      <c r="B15" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tåget, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483720</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6269912</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2014-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
